--- a/Lr14/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1.xlsx
+++ b/Lr14/Calculation Excel Sheet/variants/Transformer_Spec_7p5to1.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>10.4 A   /   18.1 A</t>
+          <t>10.8 A   /   18.2 A</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>9.5 A   /   33.4 A</t>
+          <t>9.5 A   /   33.0 A</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>9.5 A   /   33.4 A</t>
+          <t>9.5 A   /   33.0 A</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>104 mA dc load (VCC)</t>
+          <t>92 mA dc load (VCC)</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>13.15 µH    ±10 %</t>
+          <t>21.98 µH    ±10 %</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>4.67 µH    ±10 %</t>
+          <t>7.80 µH    ±10 %</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Test current 14 A, normal temperature</t>
+          <t>Test current 16 A, normal temperature</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>92  to  212 kHz</t>
+          <t>45  to  120 kHz</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Ae  ≥  116 mm²</t>
+          <t>Ae  ≥  212 mm²</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
